--- a/H2P Template Data/data/1_raw/H2P School Reference.xlsx
+++ b/H2P Template Data/data/1_raw/H2P School Reference.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RachelTavolacci\Desktop\H2P_PUBLIC\data\1_raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RachelTavolacci\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6F4378-5D5F-4E72-9ABF-99C347A49C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E321E67B-875C-427F-9487-FC9D081B21C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,7 +166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -178,31 +178,12 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -226,6 +207,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -282,27 +264,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{895D0A44-7704-4D39-88F1-5D17F123ECD4}" name="Table2" displayName="Table2" ref="A1:M5" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{895D0A44-7704-4D39-88F1-5D17F123ECD4}" name="Table2" displayName="Table2" ref="A1:M5" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:M5" xr:uid="{895D0A44-7704-4D39-88F1-5D17F123ECD4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
-    <sortCondition sortBy="fontColor" ref="B2" dxfId="5"/>
+    <sortCondition sortBy="fontColor" ref="B2" dxfId="4"/>
     <sortCondition descending="1" ref="M2"/>
     <sortCondition ref="C2"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{88AB0D58-0521-422F-8D8D-AD01921BBF58}" name="ExternalReference"/>
     <tableColumn id="2" xr3:uid="{62909606-6B6E-4EAB-B838-54E84416CEBD}" name="Region"/>
-    <tableColumn id="3" xr3:uid="{F8AC9086-336D-4C0C-8149-86891278144C}" name="School" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{9A57FB6D-80E9-4A94-8960-BD6BEFF69254}" name="Student Count" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F8AC9086-336D-4C0C-8149-86891278144C}" name="School" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{9A57FB6D-80E9-4A94-8960-BD6BEFF69254}" name="Student Count" dataDxfId="2">
+      <calculatedColumnFormula>SUM(Table2[[#This Row],[Grade 9 Count]:[Grade 12 Count]])</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="5" xr3:uid="{FF63D69A-292F-499F-88D9-564AFC142A40}" name="Grade 9 Count"/>
     <tableColumn id="6" xr3:uid="{F24AEB89-93A5-42CC-A9F8-6A8E24B971A0}" name="Grade 10 Count"/>
     <tableColumn id="7" xr3:uid="{1E19AC81-5500-4E0E-8FC6-21101B1970A5}" name="Grade 11 Count"/>
     <tableColumn id="8" xr3:uid="{5127FC8D-6683-450B-AC9C-536A3BF79563}" name="Grade 12 Count"/>
     <tableColumn id="9" xr3:uid="{CBD7A730-CBDF-4657-A56E-F89D82F58C4F}" name="Staff Count"/>
     <tableColumn id="10" xr3:uid="{6BAF990B-3356-40D6-B775-09F2CD467988}" name="Prev. Rate Completion Rate" dataCellStyle="Percent"/>
-    <tableColumn id="11" xr3:uid="{CF69F687-0CCB-4C12-B076-F4D1D5152E88}" name="Est. Completion Students" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{CF69F687-0CCB-4C12-B076-F4D1D5152E88}" name="Est. Completion Students" dataDxfId="1"/>
     <tableColumn id="12" xr3:uid="{6D3BFFAC-2B12-4693-8FBD-3DAA4AD5D72F}" name="Est. Completion Staff (Last YR total)"/>
-    <tableColumn id="13" xr3:uid="{1B315E8F-D4A4-42B1-8730-88FC512D1A01}" name="Adminstation date" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{1B315E8F-D4A4-42B1-8730-88FC512D1A01}" name="Adminstation date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -515,7 +499,8 @@
     <col min="1" max="1" width="17.1796875" customWidth="1"/>
     <col min="2" max="2" width="11.7265625" customWidth="1"/>
     <col min="3" max="3" width="29.6328125" customWidth="1"/>
-    <col min="4" max="8" width="11.7265625" customWidth="1"/>
+    <col min="4" max="4" width="23.08984375" customWidth="1"/>
+    <col min="5" max="8" width="11.7265625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="26.453125" style="7" customWidth="1"/>
     <col min="11" max="11" width="24.7265625" style="10" customWidth="1"/>
@@ -582,12 +567,25 @@
       <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="D2" s="3">
+        <f>SUM(Table2[[#This Row],[Grade 9 Count]:[Grade 12 Count]])</f>
+        <v>29</v>
+      </c>
+      <c r="E2" s="5">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5">
+        <v>9</v>
+      </c>
+      <c r="I2" s="5">
+        <v>6</v>
+      </c>
       <c r="J2" s="8"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -600,39 +598,86 @@
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="D3" s="3">
+        <f>SUM(Table2[[#This Row],[Grade 9 Count]:[Grade 12 Count]])</f>
+        <v>34</v>
+      </c>
+      <c r="E3" s="5">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>7</v>
+      </c>
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3">
+        <f>SUM(Table2[[#This Row],[Grade 9 Count]:[Grade 12 Count]])</f>
         <v>18</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="M4" s="11"/>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="M5" s="11"/>
+        <v>18</v>
+      </c>
+      <c r="D5" s="3">
+        <f>SUM(Table2[[#This Row],[Grade 9 Count]:[Grade 12 Count]])</f>
+        <v>74</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
